--- a/boc-db/insert scripts/features v0.1.xlsx
+++ b/boc-db/insert scripts/features v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DESKTOP\ERP\boc-db\insert scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831FAEF5-EA56-445A-9B28-45A1896DE126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09650608-D1D5-42D8-B526-5692772C21CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="293" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
